--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_45.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5211087.204599575</v>
+        <v>5171061.111846177</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517486</v>
+        <v>2916902.906517485</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517486</v>
+        <v>2916902.906517485</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41207873.25661963</v>
+        <v>41207873.25661964</v>
       </c>
     </row>
   </sheetData>
@@ -657,16 +657,16 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>392.9628099457239</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
         <v>403.7573722870162</v>
@@ -681,13 +681,13 @@
         <v>418.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>507.7400371911698</v>
+        <v>97.12488247690067</v>
       </c>
       <c r="L2" t="n">
+        <v>281.7754478641663</v>
+      </c>
+      <c r="M2" t="n">
         <v>814</v>
-      </c>
-      <c r="M2" t="n">
-        <v>297.9910820919849</v>
       </c>
       <c r="N2" t="n">
         <v>814</v>
@@ -699,22 +699,22 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>370.9706110579117</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>187.4578006767583</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
       </c>
       <c r="U2" t="n">
-        <v>249.2212965486107</v>
+        <v>649.2212965486107</v>
       </c>
       <c r="V2" t="n">
-        <v>229.8510241668239</v>
+        <v>629.8510241668239</v>
       </c>
       <c r="W2" t="n">
         <v>238.3734759809475</v>
@@ -745,10 +745,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>135.3518862151733</v>
       </c>
       <c r="G3" t="n">
-        <v>308.4311513056531</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617061019</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>320.9396782847086</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E5" t="n">
         <v>404.3632896068686</v>
@@ -912,40 +912,40 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>232.0824533610376</v>
+        <v>97.12488247690067</v>
       </c>
       <c r="L5" t="n">
-        <v>814.0000000000036</v>
+        <v>814</v>
       </c>
       <c r="M5" t="n">
-        <v>814</v>
+        <v>297.9910820919849</v>
       </c>
       <c r="N5" t="n">
         <v>194.5855355810472</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>216.0296191332252</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q5" t="n">
         <v>370.9706110579117</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
-        <v>530.163813431294</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -957,7 +957,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>192.2818334606677</v>
+        <v>434.9726260177878</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>148.6880250402008</v>
       </c>
       <c r="C6" t="n">
-        <v>284.6463592929431</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1027,7 +1027,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1143,19 +1143,19 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>97.12488247690055</v>
+        <v>97.12488247690067</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1164,10 +1164,10 @@
         <v>297.9910820919849</v>
       </c>
       <c r="N8" t="n">
-        <v>194.5855355810472</v>
+        <v>814</v>
       </c>
       <c r="O8" t="n">
-        <v>650.9664887921559</v>
+        <v>410.6151547142695</v>
       </c>
       <c r="P8" t="n">
         <v>814</v>
@@ -1176,16 +1176,16 @@
         <v>370.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>494.8481678023229</v>
+        <v>438.3363995050528</v>
       </c>
       <c r="T8" t="n">
         <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>341.8309294230461</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1194,7 +1194,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>192.2818334606677</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y8" t="n">
         <v>111.3174326828064</v>
@@ -1210,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>96.62571193790347</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X9" t="n">
-        <v>419.8627394453875</v>
+        <v>77.58836382881032</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1316,16 +1316,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617061022</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
       </c>
       <c r="O10" t="n">
-        <v>211.2354862247849</v>
+        <v>240.445564079015</v>
       </c>
       <c r="P10" t="n">
         <v>287.4478973282775</v>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>170.8212721783445</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>183.0096587035274</v>
@@ -1419,7 +1419,7 @@
         <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
-        <v>361.6755817285639</v>
+        <v>162.4879535237059</v>
       </c>
       <c r="U11" t="n">
         <v>424.2212965486107</v>
@@ -1434,7 +1434,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1523,19 +1523,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1553,13 +1553,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>142.2291713307485</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>125.5739916987058</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>230.9993129555745</v>
+        <v>82.41687214331128</v>
       </c>
       <c r="C14" t="n">
         <v>198.4745782429939</v>
@@ -1617,7 +1617,7 @@
         <v>153.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
         <v>157.0096587035274</v>
@@ -1653,10 +1653,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>243.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>96.00234540099424</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U14" t="n">
         <v>398.2212965486107</v>
@@ -1802,13 +1802,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>53.74128073011011</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>474.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>92.1326498274306</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1851,10 +1851,10 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>125.8896287080119</v>
+        <v>125.4590200934258</v>
       </c>
       <c r="G17" t="n">
-        <v>124.3267636724302</v>
+        <v>124.7573722870162</v>
       </c>
       <c r="H17" t="n">
         <v>129.0096587035274</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>247.1514877608905</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R19" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>125.8896287080119</v>
+        <v>125.4590200934258</v>
       </c>
       <c r="G20" t="n">
         <v>124.7573722870162</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>215.4175591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T20" t="n">
         <v>307.6755817285639</v>
@@ -2273,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>16.3474343746833</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7929984536983</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>125.4590200934258</v>
+        <v>125.8896287080119</v>
       </c>
       <c r="G23" t="n">
         <v>124.7573722870162</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T23" t="n">
         <v>307.6755817285639</v>
@@ -2507,19 +2507,19 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="Q25" t="n">
-        <v>46.45369252913971</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2553,22 +2553,22 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>81.18220435310087</v>
       </c>
       <c r="F26" t="n">
         <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
         <v>361.6755817285639</v>
@@ -2610,13 +2610,13 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>383.4369297708032</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>413.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
         <v>286.3174326828064</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>45.14518808597777</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2787,25 +2787,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>189.411675845388</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>149.6123360441489</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>404.8510241668239</v>
@@ -2945,16 +2945,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
         <v>60.53621805555548</v>
       </c>
       <c r="E31" t="n">
-        <v>55.98090483695654</v>
+        <v>33.02805474499334</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>160.7389027948726</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3045,31 +3045,31 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>8.45659138541424</v>
       </c>
       <c r="J32" t="n">
-        <v>757.6173000000416</v>
+        <v>377.7382696589747</v>
       </c>
       <c r="K32" t="n">
-        <v>10.23281455308506</v>
+        <v>10.23281455328664</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>256.9910820920272</v>
+        <v>752.1594889580108</v>
       </c>
       <c r="N32" t="n">
-        <v>153.5855355810897</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
-        <v>322.4398520017912</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000425</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>742.234599999999</v>
+        <v>329.9706110579529</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>228.7740240682207</v>
+        <v>220.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -3218,22 +3218,22 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>194.5984637871033</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>433.5163175104127</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3282,34 +3282,34 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>8.45659138541424</v>
       </c>
       <c r="J35" t="n">
-        <v>757.6173000000488</v>
+        <v>377.738269658982</v>
       </c>
       <c r="K35" t="n">
-        <v>712.6384842279116</v>
+        <v>762.3923035111844</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>289.2892533611355</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="N35" t="n">
-        <v>153.585535581097</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000498</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>329.9706110579615</v>
+        <v>329.9706110579601</v>
       </c>
       <c r="R35" t="n">
-        <v>8.456591385414804</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>203.8481678023229</v>
@@ -3449,28 +3449,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>263.8589525944566</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>23.65946653202705</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3522,28 +3522,28 @@
         <v>8.45659138541424</v>
       </c>
       <c r="J38" t="n">
-        <v>377.7382696589906</v>
+        <v>377.7382696589893</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320762618</v>
+        <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>608.8067679298266</v>
       </c>
       <c r="M38" t="n">
-        <v>654.6988358538965</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="N38" t="n">
-        <v>153.5855355811043</v>
+        <v>153.5855355811029</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000571</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>329.9706110579688</v>
+        <v>329.9706110579674</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3686,28 +3686,28 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>109.2047614405472</v>
+        <v>226.7541306595264</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,22 +3735,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>268.9993129555745</v>
+        <v>101.4184877263877</v>
       </c>
       <c r="C41" t="n">
-        <v>152.3149362112522</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>197.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
         <v>195.0096587035274</v>
@@ -3783,13 +3783,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>281.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>373.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>436.2212965486107</v>
@@ -3798,13 +3798,13 @@
         <v>416.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>425.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>379.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>298.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>213.3039220634535</v>
+        <v>334.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>253.5639999646113</v>
@@ -3877,7 +3877,7 @@
         <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>219.3731429098285</v>
+        <v>81.90670016750896</v>
       </c>
       <c r="X42" t="n">
         <v>206.8627394453875</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>15.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>13.37280983870968</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>142.4109888009625</v>
+        <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>217.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>42.35488123675749</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>221.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4035,10 +4035,10 @@
         <v>442.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>451.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>405.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>324.3174326828064</v>
@@ -4063,13 +4063,13 @@
         <v>155.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>152.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>138.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>145.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>30.12638589134853</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>220.7605511174754</v>
+        <v>58.76517960246473</v>
       </c>
       <c r="T45" t="n">
         <v>218.3577652175138</v>
@@ -4114,7 +4114,7 @@
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>245.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4190,10 +4190,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>12.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>39.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1857.446338054225</v>
+        <v>702.4077201726793</v>
       </c>
       <c r="C2" t="n">
-        <v>1460.514206795918</v>
+        <v>652.4333987151097</v>
       </c>
       <c r="D2" t="n">
-        <v>1450.070615139504</v>
+        <v>641.9898070586958</v>
       </c>
       <c r="E2" t="n">
-        <v>1041.622847859839</v>
+        <v>637.5824438194345</v>
       </c>
       <c r="F2" t="n">
         <v>632.6434249224528</v>
@@ -4324,49 +4324,49 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K2" t="n">
-        <v>741.0033264140369</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L2" t="n">
-        <v>724.6411041918145</v>
+        <v>1677.004444444444</v>
       </c>
       <c r="M2" t="n">
-        <v>1229.500011169607</v>
+        <v>1660.642222222222</v>
       </c>
       <c r="N2" t="n">
-        <v>1213.137788947385</v>
+        <v>1644.28</v>
       </c>
       <c r="O2" t="n">
-        <v>2018.997788947385</v>
+        <v>2450.14</v>
       </c>
       <c r="P2" t="n">
-        <v>2824.857788947385</v>
+        <v>3256</v>
       </c>
       <c r="Q2" t="n">
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>3160.193769896644</v>
+        <v>2813.235960095906</v>
       </c>
       <c r="T2" t="n">
-        <v>2971.632576231427</v>
+        <v>2624.67476643069</v>
       </c>
       <c r="U2" t="n">
-        <v>2719.893892848992</v>
+        <v>1968.895679007851</v>
       </c>
       <c r="V2" t="n">
-        <v>2487.721141165332</v>
+        <v>1332.682523283786</v>
       </c>
       <c r="W2" t="n">
-        <v>2246.939852295688</v>
+        <v>1091.901234414142</v>
       </c>
       <c r="X2" t="n">
-        <v>2052.715778092993</v>
+        <v>897.6771602114478</v>
       </c>
       <c r="Y2" t="n">
-        <v>1940.273926898239</v>
+        <v>785.2353090166939</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>931.509519579215</v>
+        <v>2792.129558715245</v>
       </c>
       <c r="C3" t="n">
-        <v>931.509519579215</v>
+        <v>2792.129558715245</v>
       </c>
       <c r="D3" t="n">
-        <v>931.509519579215</v>
+        <v>2792.129558715245</v>
       </c>
       <c r="E3" t="n">
-        <v>931.509519579215</v>
+        <v>2792.129558715245</v>
       </c>
       <c r="F3" t="n">
-        <v>931.509519579215</v>
+        <v>2655.410481730222</v>
       </c>
       <c r="G3" t="n">
-        <v>619.9629020987572</v>
+        <v>2655.410481730222</v>
       </c>
       <c r="H3" t="n">
-        <v>284.4395817084329</v>
+        <v>2319.887161339897</v>
       </c>
       <c r="I3" t="n">
-        <v>65.12</v>
+        <v>2100.567579631464</v>
       </c>
       <c r="J3" t="n">
-        <v>189.076520175299</v>
+        <v>2224.524099806763</v>
       </c>
       <c r="K3" t="n">
-        <v>378.2693362696824</v>
+        <v>2413.716915901147</v>
       </c>
       <c r="L3" t="n">
-        <v>649.6197978648825</v>
+        <v>2685.067377496347</v>
       </c>
       <c r="M3" t="n">
-        <v>735.7003396077417</v>
+        <v>2771.147919239206</v>
       </c>
       <c r="N3" t="n">
-        <v>868.9806242153101</v>
+        <v>2904.428203846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1108.023075899029</v>
+        <v>3143.470655530493</v>
       </c>
       <c r="P3" t="n">
-        <v>1220.552420368536</v>
+        <v>3256</v>
       </c>
       <c r="Q3" t="n">
-        <v>1220.552420368536</v>
+        <v>3081.172459504566</v>
       </c>
       <c r="R3" t="n">
-        <v>1071.791008962092</v>
+        <v>2932.411048098123</v>
       </c>
       <c r="S3" t="n">
-        <v>1004.554645361474</v>
+        <v>2865.174684497505</v>
       </c>
       <c r="T3" t="n">
-        <v>999.1427613033796</v>
+        <v>2859.76280043941</v>
       </c>
       <c r="U3" t="n">
-        <v>998.9302766971304</v>
+        <v>2859.550315833161</v>
       </c>
       <c r="V3" t="n">
-        <v>984.2730371097363</v>
+        <v>2844.893076245767</v>
       </c>
       <c r="W3" t="n">
-        <v>951.5728927563741</v>
+        <v>2812.192931892404</v>
       </c>
       <c r="X3" t="n">
-        <v>931.509519579215</v>
+        <v>2792.129558715245</v>
       </c>
       <c r="Y3" t="n">
-        <v>931.509519579215</v>
+        <v>2792.129558715245</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1266.541094834879</v>
+        <v>652.6805000684695</v>
       </c>
       <c r="C4" t="n">
-        <v>1266.541094834879</v>
+        <v>778.6825058869053</v>
       </c>
       <c r="D4" t="n">
-        <v>1266.541094834879</v>
+        <v>892.0016500119054</v>
       </c>
       <c r="E4" t="n">
-        <v>1266.541094834879</v>
+        <v>892.0016500119054</v>
       </c>
       <c r="F4" t="n">
-        <v>1266.541094834879</v>
+        <v>892.0016500119054</v>
       </c>
       <c r="G4" t="n">
-        <v>1266.541094834879</v>
+        <v>1045.408215898791</v>
       </c>
       <c r="H4" t="n">
-        <v>1436.057679994277</v>
+        <v>1214.924801058188</v>
       </c>
       <c r="I4" t="n">
-        <v>1436.057679994277</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="J4" t="n">
-        <v>1436.057679994277</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931146</v>
+        <v>1546.42211393114</v>
       </c>
       <c r="L4" t="n">
-        <v>1546.422113931146</v>
+        <v>1546.42211393114</v>
       </c>
       <c r="M4" t="n">
-        <v>1424.572001403317</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1251.657783957171</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O4" t="n">
-        <v>1008.783476806651</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P4" t="n">
-        <v>718.4320653639461</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>389.3014932168774</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
       </c>
       <c r="S4" t="n">
-        <v>87.00448252264661</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="T4" t="n">
-        <v>275.0801616814515</v>
+        <v>290.445934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>521.6313543197382</v>
+        <v>290.445934252978</v>
       </c>
       <c r="V4" t="n">
-        <v>720.4527472056841</v>
+        <v>290.445934252978</v>
       </c>
       <c r="W4" t="n">
-        <v>892.3436654653615</v>
+        <v>462.3368525126554</v>
       </c>
       <c r="X4" t="n">
-        <v>1043.374456489555</v>
+        <v>613.3676435368488</v>
       </c>
       <c r="Y4" t="n">
-        <v>1154.783757168587</v>
+        <v>613.3676435368488</v>
       </c>
     </row>
     <row r="5">
@@ -4534,46 +4534,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1106.448124213083</v>
+        <v>1358.891397260877</v>
       </c>
       <c r="C5" t="n">
-        <v>1056.473802755514</v>
+        <v>1308.917075803307</v>
       </c>
       <c r="D5" t="n">
-        <v>1046.0302110991</v>
+        <v>894.433080106489</v>
       </c>
       <c r="E5" t="n">
-        <v>637.5824438194345</v>
+        <v>485.9853128268237</v>
       </c>
       <c r="F5" t="n">
-        <v>228.6030208820488</v>
+        <v>77.00588988943801</v>
       </c>
       <c r="G5" t="n">
-        <v>224.8076953396081</v>
+        <v>73.21056434699739</v>
       </c>
       <c r="H5" t="n">
-        <v>216.7171309926107</v>
+        <v>65.12</v>
       </c>
       <c r="I5" t="n">
         <v>65.12</v>
       </c>
       <c r="J5" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K5" t="n">
-        <v>636.5532794332954</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L5" t="n">
-        <v>620.1910572110693</v>
+        <v>1139.40388673148</v>
       </c>
       <c r="M5" t="n">
-        <v>603.828834988847</v>
+        <v>1644.262793709273</v>
       </c>
       <c r="N5" t="n">
-        <v>1213.137788947385</v>
+        <v>2253.571747667811</v>
       </c>
       <c r="O5" t="n">
-        <v>2018.997788947385</v>
+        <v>2841.220011169604</v>
       </c>
       <c r="P5" t="n">
         <v>2824.857788947385</v>
@@ -4582,28 +4582,28 @@
         <v>3256</v>
       </c>
       <c r="R5" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2756.153365856239</v>
+        <v>2906.781043807457</v>
       </c>
       <c r="T5" t="n">
-        <v>2220.634362390286</v>
+        <v>2718.219850142241</v>
       </c>
       <c r="U5" t="n">
-        <v>1968.895679007851</v>
+        <v>2466.481166759806</v>
       </c>
       <c r="V5" t="n">
-        <v>1736.722927324191</v>
+        <v>2234.308415076146</v>
       </c>
       <c r="W5" t="n">
-        <v>1495.941638454547</v>
+        <v>1993.527126206502</v>
       </c>
       <c r="X5" t="n">
-        <v>1301.717564251852</v>
+        <v>1554.160837299645</v>
       </c>
       <c r="Y5" t="n">
-        <v>1189.275713057098</v>
+        <v>1441.718986104891</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>352.6415750433769</v>
+        <v>781.3195952961838</v>
       </c>
       <c r="C6" t="n">
-        <v>65.12</v>
+        <v>416.5722089875784</v>
       </c>
       <c r="D6" t="n">
         <v>65.12</v>
@@ -4658,31 +4658,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1045.724879873102</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>896.9634684666578</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>829.7271048660403</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T6" t="n">
-        <v>824.3152208079456</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>420.0623321612923</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>405.4050925738982</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>372.704948220536</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X6" t="n">
-        <v>352.6415750433769</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>352.6415750433769</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>648.4064275702968</v>
+        <v>547.5896488119156</v>
       </c>
       <c r="C7" t="n">
-        <v>648.4064275702968</v>
+        <v>673.5916546303514</v>
       </c>
       <c r="D7" t="n">
-        <v>760.1762071454287</v>
+        <v>786.9107987553515</v>
       </c>
       <c r="E7" t="n">
-        <v>878.0051113568418</v>
+        <v>904.7397029667645</v>
       </c>
       <c r="F7" t="n">
-        <v>1002.366083948777</v>
+        <v>904.7397029667645</v>
       </c>
       <c r="G7" t="n">
-        <v>1155.772649835663</v>
+        <v>1045.408215898794</v>
       </c>
       <c r="H7" t="n">
-        <v>1325.28923499506</v>
+        <v>1214.924801058192</v>
       </c>
       <c r="I7" t="n">
-        <v>1546.422113931143</v>
+        <v>1436.057679994275</v>
       </c>
       <c r="J7" t="n">
-        <v>1546.422113931143</v>
+        <v>1436.057679994275</v>
       </c>
       <c r="K7" t="n">
         <v>1546.422113931143</v>
@@ -4743,25 +4743,25 @@
         <v>65.12</v>
       </c>
       <c r="S7" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T7" t="n">
-        <v>290.445934252978</v>
+        <v>65.12</v>
       </c>
       <c r="U7" t="n">
-        <v>536.9971268912645</v>
+        <v>65.12</v>
       </c>
       <c r="V7" t="n">
-        <v>536.9971268912645</v>
+        <v>263.941392885946</v>
       </c>
       <c r="W7" t="n">
-        <v>536.9971268912645</v>
+        <v>435.8323111456234</v>
       </c>
       <c r="X7" t="n">
-        <v>536.9971268912645</v>
+        <v>435.8323111456234</v>
       </c>
       <c r="Y7" t="n">
-        <v>648.4064275702968</v>
+        <v>435.8323111456234</v>
       </c>
     </row>
     <row r="8">
@@ -4786,7 +4786,7 @@
         <v>632.6434249224528</v>
       </c>
       <c r="G8" t="n">
-        <v>224.8076953396081</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H8" t="n">
         <v>216.7171309926107</v>
@@ -4795,19 +4795,19 @@
         <v>65.12</v>
       </c>
       <c r="J8" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>772.8740581041409</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L8" t="n">
-        <v>1578.734058104141</v>
+        <v>1961.626108953703</v>
       </c>
       <c r="M8" t="n">
-        <v>2083.592965081934</v>
+        <v>2466.485015931496</v>
       </c>
       <c r="N8" t="n">
-        <v>2692.901919040472</v>
+        <v>2450.122793709274</v>
       </c>
       <c r="O8" t="n">
         <v>2841.220011169607</v>
@@ -4819,22 +4819,22 @@
         <v>3256</v>
       </c>
       <c r="R8" t="n">
-        <v>3002.587273910814</v>
+        <v>3256</v>
       </c>
       <c r="S8" t="n">
-        <v>2502.740639767053</v>
+        <v>2813.235960095906</v>
       </c>
       <c r="T8" t="n">
-        <v>1910.139042061433</v>
+        <v>2220.634362390286</v>
       </c>
       <c r="U8" t="n">
-        <v>1564.855274967447</v>
+        <v>1968.895679007851</v>
       </c>
       <c r="V8" t="n">
-        <v>1332.682523283786</v>
+        <v>1736.722927324191</v>
       </c>
       <c r="W8" t="n">
-        <v>1091.901234414142</v>
+        <v>1495.941638454547</v>
       </c>
       <c r="X8" t="n">
         <v>897.6771602114478</v>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>527.4691155388109</v>
+        <v>65.12</v>
       </c>
       <c r="C9" t="n">
-        <v>162.7217292302055</v>
+        <v>65.12</v>
       </c>
       <c r="D9" t="n">
         <v>65.12</v>
@@ -4910,16 +4910,16 @@
         <v>998.9302766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>984.2730371097363</v>
+        <v>580.2326330693322</v>
       </c>
       <c r="W9" t="n">
-        <v>951.5728927563741</v>
+        <v>143.492084675566</v>
       </c>
       <c r="X9" t="n">
-        <v>527.4691155388109</v>
+        <v>65.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>527.4691155388109</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="10">
@@ -4929,43 +4929,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>982.2165206090069</v>
+        <v>600.6766278179562</v>
       </c>
       <c r="C10" t="n">
-        <v>1108.218526427443</v>
+        <v>706.0092142429547</v>
       </c>
       <c r="D10" t="n">
-        <v>1221.537670552443</v>
+        <v>819.3283583679548</v>
       </c>
       <c r="E10" t="n">
-        <v>1221.537670552443</v>
+        <v>937.1572625793679</v>
       </c>
       <c r="F10" t="n">
-        <v>1345.898643144378</v>
+        <v>1061.518235171303</v>
       </c>
       <c r="G10" t="n">
-        <v>1376.905528771739</v>
+        <v>1214.924801058189</v>
       </c>
       <c r="H10" t="n">
-        <v>1546.422113931137</v>
+        <v>1214.924801058189</v>
       </c>
       <c r="I10" t="n">
-        <v>1546.422113931137</v>
+        <v>1436.057679994272</v>
       </c>
       <c r="J10" t="n">
-        <v>1546.422113931137</v>
+        <v>1436.057679994272</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931137</v>
+        <v>1546.42211393114</v>
       </c>
       <c r="L10" t="n">
-        <v>1522.636630943481</v>
+        <v>1546.42211393114</v>
       </c>
       <c r="M10" t="n">
-        <v>1400.786518415653</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1227.872300969507</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O10" t="n">
         <v>1014.503122964673</v>
@@ -4980,25 +4980,25 @@
         <v>65.12</v>
       </c>
       <c r="S10" t="n">
-        <v>65.12</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="T10" t="n">
-        <v>253.1956791588049</v>
+        <v>290.445934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>499.7468717970915</v>
+        <v>290.445934252978</v>
       </c>
       <c r="V10" t="n">
-        <v>698.5682646830375</v>
+        <v>489.2673271389239</v>
       </c>
       <c r="W10" t="n">
-        <v>870.4591829427148</v>
+        <v>489.2673271389239</v>
       </c>
       <c r="X10" t="n">
-        <v>870.4591829427148</v>
+        <v>489.2673271389239</v>
       </c>
       <c r="Y10" t="n">
-        <v>870.4591829427148</v>
+        <v>600.6766278179562</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>965.9697186704734</v>
+        <v>618.364549545703</v>
       </c>
       <c r="C11" t="n">
-        <v>965.9697186704734</v>
+        <v>618.364549545703</v>
       </c>
       <c r="D11" t="n">
-        <v>793.4229790963881</v>
+        <v>431.1532811216122</v>
       </c>
       <c r="E11" t="n">
-        <v>612.24793908945</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="F11" t="n">
-        <v>430.5412434247916</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="G11" t="n">
         <v>249.9782411146742</v>
@@ -5032,19 +5032,19 @@
         <v>65.12</v>
       </c>
       <c r="J11" t="n">
-        <v>456.4291130376557</v>
+        <v>177.7653900957659</v>
       </c>
       <c r="K11" t="n">
-        <v>1166.135479385524</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="L11" t="n">
-        <v>1166.135479385524</v>
+        <v>1693.331756443634</v>
       </c>
       <c r="M11" t="n">
-        <v>1676.984308114459</v>
+        <v>2204.180585172569</v>
       </c>
       <c r="N11" t="n">
-        <v>2290.204627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="O11" t="n">
         <v>2817.400904947332</v>
@@ -5062,22 +5062,22 @@
         <v>2957.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>2591.957223879615</v>
+        <v>2793.156848328967</v>
       </c>
       <c r="U11" t="n">
-        <v>2163.450863729503</v>
+        <v>2364.650488178855</v>
       </c>
       <c r="V11" t="n">
-        <v>1754.510435278166</v>
+        <v>1955.710059727517</v>
       </c>
       <c r="W11" t="n">
-        <v>1336.961469640845</v>
+        <v>1538.161094090196</v>
       </c>
       <c r="X11" t="n">
-        <v>965.9697186704734</v>
+        <v>1167.169343119825</v>
       </c>
       <c r="Y11" t="n">
-        <v>965.9697186704734</v>
+        <v>877.9598151573944</v>
       </c>
     </row>
     <row r="12">
@@ -5108,28 +5108,28 @@
         <v>65.12</v>
       </c>
       <c r="I12" t="n">
-        <v>65.12</v>
+        <v>72.91487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>267.1986282495396</v>
+        <v>215.7971006891144</v>
       </c>
       <c r="K12" t="n">
-        <v>679.141444343923</v>
+        <v>627.7399167834978</v>
       </c>
       <c r="L12" t="n">
-        <v>1173.241905939123</v>
+        <v>1121.840378378698</v>
       </c>
       <c r="M12" t="n">
-        <v>1482.072447681982</v>
+        <v>1430.670920121557</v>
       </c>
       <c r="N12" t="n">
-        <v>1838.102732289551</v>
+        <v>1786.701204729125</v>
       </c>
       <c r="O12" t="n">
-        <v>2299.895183973269</v>
+        <v>2248.493656412844</v>
       </c>
       <c r="P12" t="n">
-        <v>2635.174528442776</v>
+        <v>2583.773000882351</v>
       </c>
       <c r="Q12" t="n">
         <v>2635.174528442776</v>
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>223.5645793478402</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="C13" t="n">
-        <v>175.3572595013304</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="D13" t="n">
-        <v>175.3572595013304</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="E13" t="n">
-        <v>118.8108909791521</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="F13" t="n">
-        <v>68.92921828446326</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="G13" t="n">
-        <v>68.92921828446326</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="H13" t="n">
+        <v>173.6223697938169</v>
+      </c>
+      <c r="I13" t="n">
+        <v>221.5052487298998</v>
+      </c>
+      <c r="J13" t="n">
+        <v>409.3389893823512</v>
+      </c>
+      <c r="K13" t="n">
+        <v>409.3389893823512</v>
+      </c>
+      <c r="L13" t="n">
+        <v>208.7858296270187</v>
+      </c>
+      <c r="M13" t="n">
+        <v>208.7858296270187</v>
+      </c>
+      <c r="N13" t="n">
         <v>65.12</v>
       </c>
-      <c r="I13" t="n">
-        <v>113.0028789360829</v>
-      </c>
-      <c r="J13" t="n">
-        <v>300.8366195885342</v>
-      </c>
-      <c r="K13" t="n">
-        <v>300.8366195885342</v>
-      </c>
-      <c r="L13" t="n">
-        <v>300.8366195885342</v>
-      </c>
-      <c r="M13" t="n">
-        <v>300.8366195885342</v>
-      </c>
-      <c r="N13" t="n">
-        <v>300.8366195885342</v>
-      </c>
       <c r="O13" t="n">
-        <v>300.8366195885342</v>
+        <v>65.12</v>
       </c>
       <c r="P13" t="n">
-        <v>300.8366195885342</v>
+        <v>65.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>173.9942037312557</v>
+        <v>65.12</v>
       </c>
       <c r="R13" t="n">
-        <v>173.9942037312557</v>
+        <v>65.12</v>
       </c>
       <c r="S13" t="n">
-        <v>173.9942037312557</v>
+        <v>65.12</v>
       </c>
       <c r="T13" t="n">
-        <v>188.8198828900605</v>
+        <v>79.94567915880486</v>
       </c>
       <c r="U13" t="n">
-        <v>262.1210755283471</v>
+        <v>153.2468717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>287.6924684142931</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>286.3057918095358</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="X13" t="n">
-        <v>286.3057918095358</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="Y13" t="n">
-        <v>286.3057918095358</v>
+        <v>177.4315880782802</v>
       </c>
     </row>
     <row r="14">
@@ -5245,19 +5245,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>895.5001121224765</v>
+        <v>1049.800488169968</v>
       </c>
       <c r="C14" t="n">
-        <v>695.0207401598564</v>
+        <v>849.3211162073476</v>
       </c>
       <c r="D14" t="n">
-        <v>534.0720979983919</v>
+        <v>688.3724740458831</v>
       </c>
       <c r="E14" t="n">
-        <v>379.1596842540801</v>
+        <v>533.4600603015713</v>
       </c>
       <c r="F14" t="n">
-        <v>223.7156148520479</v>
+        <v>378.015990899539</v>
       </c>
       <c r="G14" t="n">
         <v>223.7156148520479</v>
@@ -5275,13 +5275,13 @@
         <v>456.4291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>887.4717564436343</v>
+        <v>1262.289113037656</v>
       </c>
       <c r="M14" t="n">
-        <v>1398.320585172569</v>
+        <v>1773.137941766591</v>
       </c>
       <c r="N14" t="n">
-        <v>2011.540904947332</v>
+        <v>2386.358261541354</v>
       </c>
       <c r="O14" t="n">
         <v>2817.400904947332</v>
@@ -5296,25 +5296,25 @@
         <v>3256</v>
       </c>
       <c r="S14" t="n">
-        <v>3009.688719391593</v>
+        <v>3256</v>
       </c>
       <c r="T14" t="n">
-        <v>2912.716653329983</v>
+        <v>2916.933755829733</v>
       </c>
       <c r="U14" t="n">
-        <v>2510.472919442497</v>
+        <v>2514.690021942248</v>
       </c>
       <c r="V14" t="n">
-        <v>2127.795117253786</v>
+        <v>2132.012219753537</v>
       </c>
       <c r="W14" t="n">
-        <v>1736.508777879091</v>
+        <v>1740.725880378842</v>
       </c>
       <c r="X14" t="n">
-        <v>1391.779653171346</v>
+        <v>1395.996755671097</v>
       </c>
       <c r="Y14" t="n">
-        <v>1128.832751471542</v>
+        <v>1133.049853971292</v>
       </c>
     </row>
     <row r="15">
@@ -5354,16 +5354,16 @@
         <v>660.2942142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>1096.180984439304</v>
+        <v>931.6446758324473</v>
       </c>
       <c r="M15" t="n">
-        <v>1182.261526182163</v>
+        <v>1266.215217575306</v>
       </c>
       <c r="N15" t="n">
-        <v>1315.541810789732</v>
+        <v>1564.031810789731</v>
       </c>
       <c r="O15" t="n">
-        <v>1803.074262473451</v>
+        <v>2051.564262473451</v>
       </c>
       <c r="P15" t="n">
         <v>2164.093606942957</v>
@@ -5445,10 +5445,10 @@
         <v>599.0397446017254</v>
       </c>
       <c r="P16" t="n">
-        <v>544.7556226521192</v>
+        <v>158.1832826539703</v>
       </c>
       <c r="Q16" t="n">
-        <v>65.12</v>
+        <v>158.1832826539703</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5494,7 +5494,7 @@
         <v>448.1766172565348</v>
       </c>
       <c r="F17" t="n">
-        <v>321.0153761373309</v>
+        <v>321.4503343338824</v>
       </c>
       <c r="G17" t="n">
         <v>195.4327865692196</v>
@@ -5509,22 +5509,22 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>520.2108514963016</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>1326.070851496302</v>
+        <v>1262.289113037656</v>
       </c>
       <c r="M17" t="n">
-        <v>1836.919680225237</v>
+        <v>1773.137941766591</v>
       </c>
       <c r="N17" t="n">
-        <v>2450.14</v>
+        <v>2386.358261541354</v>
       </c>
       <c r="O17" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5588,22 +5588,22 @@
         <v>250.3313981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>439.5242142372473</v>
+        <v>715.7342142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>710.8746758324473</v>
+        <v>1246.060087757305</v>
       </c>
       <c r="M18" t="n">
-        <v>796.9552175753066</v>
+        <v>1332.140629500164</v>
       </c>
       <c r="N18" t="n">
-        <v>1084.349386547307</v>
+        <v>1465.420914107732</v>
       </c>
       <c r="O18" t="n">
-        <v>1323.391838231026</v>
+        <v>1704.463365791451</v>
       </c>
       <c r="P18" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q18" t="n">
         <v>1816.992710260958</v>
@@ -5640,55 +5640,55 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>414.3442160506673</v>
+        <v>422.5399739669084</v>
       </c>
       <c r="C19" t="n">
-        <v>420.5562218691031</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="D19" t="n">
-        <v>420.5562218691031</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="E19" t="n">
-        <v>420.5562218691031</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="F19" t="n">
-        <v>425.1271944610386</v>
+        <v>433.3229523772797</v>
       </c>
       <c r="G19" t="n">
-        <v>458.7437603479239</v>
+        <v>466.939518264165</v>
       </c>
       <c r="H19" t="n">
-        <v>508.4703455073215</v>
+        <v>516.6661034235625</v>
       </c>
       <c r="I19" t="n">
-        <v>609.8132244434044</v>
+        <v>618.0089823596454</v>
       </c>
       <c r="J19" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="K19" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="L19" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M19" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N19" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O19" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P19" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q19" t="n">
-        <v>601.4589976606127</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R19" t="n">
-        <v>149.3356360634903</v>
+        <v>65.12</v>
       </c>
       <c r="S19" t="n">
         <v>65.12</v>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>880.1035184729978</v>
+        <v>879.6685602764463</v>
       </c>
       <c r="C20" t="n">
-        <v>707.906974793206</v>
+        <v>707.4720165966545</v>
       </c>
       <c r="D20" t="n">
-        <v>575.2411609145698</v>
+        <v>574.8062027180183</v>
       </c>
       <c r="E20" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172565348</v>
       </c>
       <c r="F20" t="n">
         <v>321.4503343338824</v>
@@ -5743,22 +5743,22 @@
         <v>65.12</v>
       </c>
       <c r="J20" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K20" t="n">
-        <v>456.4291130376557</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L20" t="n">
-        <v>1262.289113037656</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M20" t="n">
-        <v>1773.137941766591</v>
+        <v>2091.535195076804</v>
       </c>
       <c r="N20" t="n">
-        <v>2386.358261541354</v>
+        <v>2704.755514851567</v>
       </c>
       <c r="O20" t="n">
-        <v>2450.14</v>
+        <v>3256</v>
       </c>
       <c r="P20" t="n">
         <v>3256</v>
@@ -5770,25 +5770,25 @@
         <v>3256</v>
       </c>
       <c r="S20" t="n">
-        <v>3038.406505870973</v>
+        <v>3037.971547674421</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.623089983534</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.662184378877</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V20" t="n">
-        <v>1999.267210472994</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W20" t="n">
-        <v>1636.263699381128</v>
+        <v>1635.828741184576</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.817402956211</v>
+        <v>1319.382444759659</v>
       </c>
       <c r="Y20" t="n">
-        <v>1085.153329539235</v>
+        <v>1084.718371342683</v>
       </c>
     </row>
     <row r="21">
@@ -5831,13 +5831,13 @@
         <v>710.8746758324473</v>
       </c>
       <c r="M21" t="n">
-        <v>796.9552175753066</v>
+        <v>951.0691019397386</v>
       </c>
       <c r="N21" t="n">
-        <v>930.2355021828749</v>
+        <v>1360.559386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1323.391838231026</v>
+        <v>1599.601838231026</v>
       </c>
       <c r="P21" t="n">
         <v>1712.131182700533</v>
@@ -5916,13 +5916,13 @@
         <v>859.3027230120967</v>
       </c>
       <c r="O22" t="n">
-        <v>859.3027230120967</v>
+        <v>494.2061936393544</v>
       </c>
       <c r="P22" t="n">
-        <v>446.72908934717</v>
+        <v>81.63255997442758</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.72908934717</v>
+        <v>65.12</v>
       </c>
       <c r="R22" t="n">
         <v>65.12</v>
@@ -5956,16 +5956,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>879.6685602764463</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C23" t="n">
-        <v>707.4720165966545</v>
+        <v>707.906974793206</v>
       </c>
       <c r="D23" t="n">
-        <v>574.8062027180183</v>
+        <v>575.2411609145698</v>
       </c>
       <c r="E23" t="n">
-        <v>448.1766172565348</v>
+        <v>448.6115754530863</v>
       </c>
       <c r="F23" t="n">
         <v>321.4503343338824</v>
@@ -5980,25 +5980,25 @@
         <v>65.12</v>
       </c>
       <c r="J23" t="n">
-        <v>321.3533138773685</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>1031.059680225237</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1836.919680225237</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>1836.919680225237</v>
+        <v>967.2779417665907</v>
       </c>
       <c r="N23" t="n">
-        <v>2450.14</v>
+        <v>1580.498261541354</v>
       </c>
       <c r="O23" t="n">
-        <v>3256</v>
+        <v>2386.358261541354</v>
       </c>
       <c r="P23" t="n">
-        <v>3256</v>
+        <v>3192.218261541354</v>
       </c>
       <c r="Q23" t="n">
         <v>3256</v>
@@ -6007,25 +6007,25 @@
         <v>3256</v>
       </c>
       <c r="S23" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W23" t="n">
-        <v>1635.828741184576</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y23" t="n">
-        <v>1084.718371342683</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="24">
@@ -6059,19 +6059,19 @@
         <v>126.374877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>526.5413981428638</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>715.7342142372472</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>1141.198560196879</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M24" t="n">
-        <v>1227.279101939739</v>
+        <v>796.9552175753066</v>
       </c>
       <c r="N24" t="n">
-        <v>1360.559386547307</v>
+        <v>1206.445502182875</v>
       </c>
       <c r="O24" t="n">
         <v>1599.601838231026</v>
@@ -6150,16 +6150,16 @@
         <v>859.3027230120967</v>
       </c>
       <c r="N25" t="n">
-        <v>564.1662833437281</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O25" t="n">
-        <v>564.1662833437281</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P25" t="n">
-        <v>564.1662833437281</v>
+        <v>516.472794369291</v>
       </c>
       <c r="Q25" t="n">
-        <v>517.2433615971223</v>
+        <v>65.12</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1204.096245745725</v>
+        <v>512.760190708043</v>
       </c>
       <c r="C26" t="n">
-        <v>977.3542475204788</v>
+        <v>512.760190708043</v>
       </c>
       <c r="D26" t="n">
-        <v>790.1429790963881</v>
+        <v>325.5489222839523</v>
       </c>
       <c r="E26" t="n">
-        <v>608.9679390894501</v>
+        <v>243.5466956646584</v>
       </c>
       <c r="F26" t="n">
-        <v>427.2612434247916</v>
+        <v>61.84</v>
       </c>
       <c r="G26" t="n">
-        <v>246.6982411146742</v>
+        <v>61.84</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6220,49 +6220,49 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>453.1491130376558</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>453.1491130376558</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>963.9979417665908</v>
+        <v>1673.704308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>1577.218261541354</v>
+        <v>2286.924627889222</v>
       </c>
       <c r="O26" t="n">
-        <v>2326.729999999972</v>
+        <v>3052.194627889249</v>
       </c>
       <c r="P26" t="n">
-        <v>3092</v>
+        <v>3052.194627889249</v>
       </c>
       <c r="Q26" t="n">
         <v>3092</v>
       </c>
       <c r="R26" t="n">
-        <v>3092</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>3092</v>
+        <v>2793.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>2726.671129567107</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2298.164769416995</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>1910.854739345477</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1493.305773708156</v>
+        <v>1172.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1493.305773708156</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>1204.096245745725</v>
+        <v>512.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6302,13 +6302,13 @@
         <v>828.2842142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1118.560378378698</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1427.390920121557</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.421204729126</v>
+        <v>1987.245502182875</v>
       </c>
       <c r="O27" t="n">
         <v>2245.213656412845</v>
@@ -6381,22 +6381,22 @@
         <v>406.0589893823512</v>
       </c>
       <c r="L28" t="n">
-        <v>406.0589893823512</v>
+        <v>360.457789295505</v>
       </c>
       <c r="M28" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="N28" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="O28" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="P28" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="R28" t="n">
         <v>61.84</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>253.1649250963515</v>
+        <v>941.2665508581547</v>
       </c>
       <c r="C29" t="n">
-        <v>61.84</v>
+        <v>941.2665508581547</v>
       </c>
       <c r="D29" t="n">
-        <v>61.84</v>
+        <v>790.1429790963881</v>
       </c>
       <c r="E29" t="n">
-        <v>61.84</v>
+        <v>608.9679390894501</v>
       </c>
       <c r="F29" t="n">
-        <v>61.84</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="G29" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6454,25 +6454,25 @@
         <v>61.84</v>
       </c>
       <c r="J29" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K29" t="n">
-        <v>453.1491130376558</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="L29" t="n">
-        <v>453.1491130376558</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="M29" t="n">
-        <v>963.9979417665908</v>
+        <v>1282.395195076803</v>
       </c>
       <c r="N29" t="n">
-        <v>1577.218261541354</v>
+        <v>1895.615514851567</v>
       </c>
       <c r="O29" t="n">
-        <v>2326.729999999965</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P29" t="n">
-        <v>3092</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>3092</v>
@@ -6487,19 +6487,19 @@
         <v>2427.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>1999.450863729503</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="V29" t="n">
-        <v>1590.510435278166</v>
+        <v>2019.016795428278</v>
       </c>
       <c r="W29" t="n">
-        <v>1172.961469640845</v>
+        <v>1601.467829790957</v>
       </c>
       <c r="X29" t="n">
-        <v>801.9697186704736</v>
+        <v>1230.476078820585</v>
       </c>
       <c r="Y29" t="n">
-        <v>512.760190708043</v>
+        <v>941.2665508581547</v>
       </c>
     </row>
     <row r="30">
@@ -6530,19 +6530,19 @@
         <v>61.84</v>
       </c>
       <c r="I30" t="n">
-        <v>61.84</v>
+        <v>69.63487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>212.5171006891147</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>624.4599167834981</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L30" t="n">
-        <v>1118.560378378698</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M30" t="n">
-        <v>1427.390920121557</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N30" t="n">
         <v>1783.421204729126</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>183.3432818122532</v>
+        <v>208.3659045961739</v>
       </c>
       <c r="C31" t="n">
-        <v>183.3432818122532</v>
+        <v>160.1585847496641</v>
       </c>
       <c r="D31" t="n">
-        <v>122.1955868066416</v>
+        <v>99.01088974405249</v>
       </c>
       <c r="E31" t="n">
         <v>65.64921828446326</v>
@@ -6615,49 +6615,49 @@
         <v>297.5566195885342</v>
       </c>
       <c r="K31" t="n">
-        <v>233.3942218096018</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="L31" t="n">
-        <v>233.3942218096018</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="M31" t="n">
-        <v>233.3942218096018</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="N31" t="n">
-        <v>233.3942218096018</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="O31" t="n">
-        <v>233.3942218096018</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="P31" t="n">
-        <v>233.3942218096018</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="Q31" t="n">
-        <v>233.3942218096018</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="R31" t="n">
-        <v>71.03169373397299</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="S31" t="n">
-        <v>71.03169373397299</v>
+        <v>158.7955289795893</v>
       </c>
       <c r="T31" t="n">
-        <v>85.85737289277785</v>
+        <v>173.6212081383942</v>
       </c>
       <c r="U31" t="n">
-        <v>159.1585655310645</v>
+        <v>246.9224007766808</v>
       </c>
       <c r="V31" t="n">
-        <v>184.7299584170105</v>
+        <v>272.4937936626268</v>
       </c>
       <c r="W31" t="n">
-        <v>183.3432818122532</v>
+        <v>271.1071170578695</v>
       </c>
       <c r="X31" t="n">
-        <v>183.3432818122532</v>
+        <v>271.1071170578695</v>
       </c>
       <c r="Y31" t="n">
-        <v>183.3432818122532</v>
+        <v>271.1071170578695</v>
       </c>
     </row>
     <row r="32">
@@ -6667,49 +6667,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>804.0962457457251</v>
+        <v>812.6382572461436</v>
       </c>
       <c r="C32" t="n">
-        <v>644.0209141871454</v>
+        <v>652.5629256875638</v>
       </c>
       <c r="D32" t="n">
-        <v>523.4763124297214</v>
+        <v>532.0183239301398</v>
       </c>
       <c r="E32" t="n">
-        <v>408.96793908945</v>
+        <v>417.5099505898684</v>
       </c>
       <c r="F32" t="n">
-        <v>293.9279100914582</v>
+        <v>302.4699215918766</v>
       </c>
       <c r="G32" t="n">
-        <v>180.0315744480075</v>
+        <v>188.5735859484259</v>
       </c>
       <c r="H32" t="n">
-        <v>61.84</v>
+        <v>70.38201150041843</v>
       </c>
       <c r="I32" t="n">
         <v>61.84</v>
       </c>
       <c r="J32" t="n">
-        <v>61.84</v>
+        <v>445.5561922637026</v>
       </c>
       <c r="K32" t="n">
-        <v>771.340676439175</v>
+        <v>1155.056868702874</v>
       </c>
       <c r="L32" t="n">
-        <v>1536.610676439175</v>
+        <v>1920.326868702874</v>
       </c>
       <c r="M32" t="n">
-        <v>2042.293724831109</v>
+        <v>1925.839809149368</v>
       </c>
       <c r="N32" t="n">
-        <v>2652.426820203787</v>
+        <v>1910.301728341286</v>
       </c>
       <c r="O32" t="n">
-        <v>3092</v>
+        <v>1894.763647533204</v>
       </c>
       <c r="P32" t="n">
-        <v>3076.461919191876</v>
+        <v>2660.033647533245</v>
       </c>
       <c r="Q32" t="n">
         <v>3092</v>
@@ -6736,7 +6736,7 @@
         <v>1228.109717486932</v>
       </c>
       <c r="Y32" t="n">
-        <v>997.0248446907499</v>
+        <v>1005.566856191168</v>
       </c>
     </row>
     <row r="33">
@@ -6767,22 +6767,22 @@
         <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>61.84</v>
+        <v>134.974877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>185.796520175299</v>
+        <v>547.0213981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>374.9893362696823</v>
+        <v>736.2142142372472</v>
       </c>
       <c r="L33" t="n">
-        <v>646.3397978648825</v>
+        <v>1007.564675832447</v>
       </c>
       <c r="M33" t="n">
-        <v>732.4203396077418</v>
+        <v>1093.645217575307</v>
       </c>
       <c r="N33" t="n">
-        <v>1153.79062421531</v>
+        <v>1226.925502182875</v>
       </c>
       <c r="O33" t="n">
         <v>1519.36518397327</v>
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>486.0066123122328</v>
+        <v>486.0066123122566</v>
       </c>
       <c r="C34" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306923</v>
       </c>
       <c r="D34" t="n">
-        <v>509.5077622556687</v>
+        <v>509.5077622556924</v>
       </c>
       <c r="E34" t="n">
-        <v>519.4266664670818</v>
+        <v>519.4266664671054</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590409</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459262</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053238</v>
       </c>
       <c r="I34" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414067</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693858</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="L34" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="M34" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="N34" t="n">
-        <v>815.2677387952449</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="O34" t="n">
-        <v>462.2924215437147</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="P34" t="n">
-        <v>61.84</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.84</v>
+        <v>573.9365734181883</v>
       </c>
       <c r="R34" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S34" t="n">
         <v>61.84</v>
@@ -6904,46 +6904,46 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>804.0962457457251</v>
+        <v>812.6382572461436</v>
       </c>
       <c r="C35" t="n">
-        <v>644.0209141871454</v>
+        <v>652.5629256875638</v>
       </c>
       <c r="D35" t="n">
-        <v>523.4763124297214</v>
+        <v>532.0183239301398</v>
       </c>
       <c r="E35" t="n">
-        <v>408.96793908945</v>
+        <v>417.5099505898684</v>
       </c>
       <c r="F35" t="n">
-        <v>293.9279100914582</v>
+        <v>302.4699215918766</v>
       </c>
       <c r="G35" t="n">
-        <v>180.0315744480075</v>
+        <v>188.5735859484259</v>
       </c>
       <c r="H35" t="n">
-        <v>61.84</v>
+        <v>70.38201150041843</v>
       </c>
       <c r="I35" t="n">
         <v>61.84</v>
       </c>
       <c r="J35" t="n">
-        <v>61.84</v>
+        <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>61.84</v>
+        <v>430.2313368698917</v>
       </c>
       <c r="L35" t="n">
-        <v>827.1099999999999</v>
+        <v>1160.569809149313</v>
       </c>
       <c r="M35" t="n">
-        <v>1300.168632968599</v>
+        <v>1145.031728341231</v>
       </c>
       <c r="N35" t="n">
-        <v>1910.301728341278</v>
+        <v>1129.493647533149</v>
       </c>
       <c r="O35" t="n">
-        <v>1894.763647533196</v>
+        <v>1894.763647533197</v>
       </c>
       <c r="P35" t="n">
         <v>2660.033647533245</v>
@@ -6952,28 +6952,28 @@
         <v>3092</v>
       </c>
       <c r="R35" t="n">
-        <v>3083.457988499581</v>
+        <v>3092</v>
       </c>
       <c r="S35" t="n">
-        <v>2877.550748295214</v>
+        <v>2886.092759795633</v>
       </c>
       <c r="T35" t="n">
-        <v>2578.888544528988</v>
+        <v>2587.430556029407</v>
       </c>
       <c r="U35" t="n">
-        <v>2217.048851045543</v>
+        <v>2225.590862545962</v>
       </c>
       <c r="V35" t="n">
-        <v>1874.775089260873</v>
+        <v>1883.317100761291</v>
       </c>
       <c r="W35" t="n">
-        <v>1523.892790290219</v>
+        <v>1532.434801790637</v>
       </c>
       <c r="X35" t="n">
-        <v>1219.567705986514</v>
+        <v>1228.109717486932</v>
       </c>
       <c r="Y35" t="n">
-        <v>997.0248446907499</v>
+        <v>1005.566856191168</v>
       </c>
     </row>
     <row r="36">
@@ -7004,28 +7004,28 @@
         <v>61.84</v>
       </c>
       <c r="I36" t="n">
-        <v>61.84</v>
+        <v>134.974877967565</v>
       </c>
       <c r="J36" t="n">
-        <v>185.796520175299</v>
+        <v>258.9313981428639</v>
       </c>
       <c r="K36" t="n">
-        <v>374.9893362696823</v>
+        <v>448.1242142372473</v>
       </c>
       <c r="L36" t="n">
-        <v>646.3397978648825</v>
+        <v>719.4746758324475</v>
       </c>
       <c r="M36" t="n">
-        <v>742.2109201215573</v>
+        <v>1093.645217575307</v>
       </c>
       <c r="N36" t="n">
-        <v>875.4912047291256</v>
+        <v>1226.925502182875</v>
       </c>
       <c r="O36" t="n">
-        <v>1114.533656412844</v>
+        <v>1465.967953866594</v>
       </c>
       <c r="P36" t="n">
-        <v>1515.153000882351</v>
+        <v>1578.497298336101</v>
       </c>
       <c r="Q36" t="n">
         <v>1631.894528442776</v>
@@ -7092,25 +7092,25 @@
         <v>1011.831843630726</v>
       </c>
       <c r="L37" t="n">
-        <v>1011.831843630726</v>
+        <v>877.9453505420606</v>
       </c>
       <c r="M37" t="n">
-        <v>1011.831843630726</v>
+        <v>877.9453505420606</v>
       </c>
       <c r="N37" t="n">
-        <v>728.8166160835699</v>
+        <v>877.9453505420606</v>
       </c>
       <c r="O37" t="n">
-        <v>462.2924215437147</v>
+        <v>524.9700332905304</v>
       </c>
       <c r="P37" t="n">
-        <v>61.84</v>
+        <v>524.9700332905304</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.84</v>
+        <v>85.73845104245157</v>
       </c>
       <c r="R37" t="n">
-        <v>61.84</v>
+        <v>85.73845104245157</v>
       </c>
       <c r="S37" t="n">
         <v>61.84</v>
@@ -7168,19 +7168,19 @@
         <v>445.5561922637023</v>
       </c>
       <c r="K38" t="n">
-        <v>430.9405883765127</v>
+        <v>430.0181114556214</v>
       </c>
       <c r="L38" t="n">
-        <v>1196.210588376513</v>
+        <v>534.8986329685391</v>
       </c>
       <c r="M38" t="n">
-        <v>1300.168632968593</v>
+        <v>519.3605521604571</v>
       </c>
       <c r="N38" t="n">
-        <v>1910.301728341271</v>
+        <v>1129.493647533136</v>
       </c>
       <c r="O38" t="n">
-        <v>1894.763647533189</v>
+        <v>1894.763647533191</v>
       </c>
       <c r="P38" t="n">
         <v>2660.033647533246</v>
@@ -7241,22 +7241,22 @@
         <v>61.84</v>
       </c>
       <c r="I39" t="n">
-        <v>134.974877967565</v>
+        <v>71.6305805138154</v>
       </c>
       <c r="J39" t="n">
-        <v>258.9313981428639</v>
+        <v>195.5871006891144</v>
       </c>
       <c r="K39" t="n">
-        <v>448.1242142372473</v>
+        <v>384.7799167834978</v>
       </c>
       <c r="L39" t="n">
-        <v>719.4746758324475</v>
+        <v>656.1303783786979</v>
       </c>
       <c r="M39" t="n">
-        <v>805.5552175753068</v>
+        <v>742.2109201215571</v>
       </c>
       <c r="N39" t="n">
-        <v>938.8355021828751</v>
+        <v>875.4912047291255</v>
       </c>
       <c r="O39" t="n">
         <v>1402.623656412844</v>
@@ -7299,55 +7299,55 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>486.0066123122601</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>504.0986181306959</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D40" t="n">
-        <v>509.507762255696</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E40" t="n">
-        <v>519.426666467109</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F40" t="n">
-        <v>535.8776390590446</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G40" t="n">
-        <v>581.3742049459298</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H40" t="n">
-        <v>642.9807901053274</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I40" t="n">
-        <v>756.2036690414103</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1009.377409693862</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L40" t="n">
-        <v>1011.83184363073</v>
+        <v>877.945350542037</v>
       </c>
       <c r="M40" t="n">
-        <v>1011.83184363073</v>
+        <v>645.9942279131988</v>
       </c>
       <c r="N40" t="n">
-        <v>1011.83184363073</v>
+        <v>362.9790003660423</v>
       </c>
       <c r="O40" t="n">
-        <v>1011.83184363073</v>
+        <v>362.9790003660423</v>
       </c>
       <c r="P40" t="n">
-        <v>611.3794220870154</v>
+        <v>362.9790003660423</v>
       </c>
       <c r="Q40" t="n">
-        <v>172.1478398389366</v>
+        <v>362.9790003660423</v>
       </c>
       <c r="R40" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S40" t="n">
         <v>61.84</v>
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>612.0054047016458</v>
+        <v>1276.823518472998</v>
       </c>
       <c r="C41" t="n">
-        <v>458.1519337811891</v>
+        <v>1037.960308126539</v>
       </c>
       <c r="D41" t="n">
-        <v>258.8194532358863</v>
+        <v>838.6278275812365</v>
       </c>
       <c r="E41" t="n">
-        <v>258.8194532358863</v>
+        <v>645.3315754530863</v>
       </c>
       <c r="F41" t="n">
-        <v>258.8194532358863</v>
+        <v>451.5036676672158</v>
       </c>
       <c r="G41" t="n">
         <v>258.8194532358863</v>
@@ -7405,19 +7405,19 @@
         <v>61.84</v>
       </c>
       <c r="K41" t="n">
-        <v>771.5463663478683</v>
+        <v>61.84</v>
       </c>
       <c r="L41" t="n">
-        <v>1529.331756443634</v>
+        <v>61.84</v>
       </c>
       <c r="M41" t="n">
-        <v>2040.180585172569</v>
+        <v>572.6888287289351</v>
       </c>
       <c r="N41" t="n">
-        <v>2653.400904947332</v>
+        <v>1185.909148503698</v>
       </c>
       <c r="O41" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.13090494727</v>
       </c>
       <c r="P41" t="n">
         <v>2653.400904947332</v>
@@ -7426,28 +7426,28 @@
         <v>3092</v>
       </c>
       <c r="R41" t="n">
-        <v>3092</v>
+        <v>3053.738789062329</v>
       </c>
       <c r="S41" t="n">
-        <v>2807.304881007754</v>
+        <v>3053.738789062329</v>
       </c>
       <c r="T41" t="n">
-        <v>2429.854798453649</v>
+        <v>3053.738789062329</v>
       </c>
       <c r="U41" t="n">
-        <v>1989.227226182325</v>
+        <v>2613.111216791005</v>
       </c>
       <c r="V41" t="n">
-        <v>1568.165585609776</v>
+        <v>2192.049576218456</v>
       </c>
       <c r="W41" t="n">
-        <v>1568.165585609776</v>
+        <v>1762.379398459923</v>
       </c>
       <c r="X41" t="n">
-        <v>1185.052622518192</v>
+        <v>1379.266435368339</v>
       </c>
       <c r="Y41" t="n">
-        <v>883.7218824345495</v>
+        <v>1379.266435368339</v>
       </c>
     </row>
     <row r="42">
@@ -7496,28 +7496,28 @@
         <v>1920.05062421531</v>
       </c>
       <c r="O42" t="n">
-        <v>2369.963075899029</v>
+        <v>2316.104912118934</v>
       </c>
       <c r="P42" t="n">
-        <v>2656.16745609692</v>
+        <v>2639.504256588441</v>
       </c>
       <c r="Q42" t="n">
-        <v>2695.688983657345</v>
+        <v>2679.025784148866</v>
       </c>
       <c r="R42" t="n">
-        <v>2480.230476522543</v>
+        <v>2341.375483853533</v>
       </c>
       <c r="S42" t="n">
-        <v>2224.105224033037</v>
+        <v>2085.250231364027</v>
       </c>
       <c r="T42" t="n">
-        <v>2029.804451086053</v>
+        <v>1890.949458417043</v>
       </c>
       <c r="U42" t="n">
-        <v>1840.703077590915</v>
+        <v>1701.848084921905</v>
       </c>
       <c r="V42" t="n">
-        <v>1637.156949114632</v>
+        <v>1498.301956445622</v>
       </c>
       <c r="W42" t="n">
         <v>1415.567915872381</v>
@@ -7536,22 +7536,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="C43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="D43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="E43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="F43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="G43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="H43" t="n">
         <v>61.84</v>
@@ -7560,52 +7560,52 @@
         <v>61.84</v>
       </c>
       <c r="J43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="K43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="L43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="M43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="N43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="O43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="P43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="Q43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="R43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="S43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="T43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="U43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="V43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="W43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="X43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="Y43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>61.84</v>
+        <v>773.0187730171751</v>
       </c>
       <c r="C44" t="n">
-        <v>61.84</v>
+        <v>773.0187730171751</v>
       </c>
       <c r="D44" t="n">
-        <v>61.84</v>
+        <v>547.423666209246</v>
       </c>
       <c r="E44" t="n">
-        <v>61.84</v>
+        <v>327.8647878184696</v>
       </c>
       <c r="F44" t="n">
-        <v>61.84</v>
+        <v>285.0820794985125</v>
       </c>
       <c r="G44" t="n">
-        <v>61.84</v>
+        <v>285.0820794985125</v>
       </c>
       <c r="H44" t="n">
         <v>61.84</v>
@@ -7639,19 +7639,19 @@
         <v>61.84</v>
       </c>
       <c r="J44" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K44" t="n">
-        <v>1162.855479385524</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="L44" t="n">
-        <v>1928.125479385524</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="M44" t="n">
-        <v>1928.125479385524</v>
+        <v>1282.395195076803</v>
       </c>
       <c r="N44" t="n">
-        <v>2541.345799160287</v>
+        <v>1895.615514851567</v>
       </c>
       <c r="O44" t="n">
         <v>2653.400904947332</v>
@@ -7678,13 +7678,13 @@
         <v>1398.591243358974</v>
       </c>
       <c r="W44" t="n">
-        <v>942.6584393378148</v>
+        <v>1398.591243358974</v>
       </c>
       <c r="X44" t="n">
-        <v>533.2828499836049</v>
+        <v>1398.591243358974</v>
       </c>
       <c r="Y44" t="n">
-        <v>205.6894836373359</v>
+        <v>1070.997877012705</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>587.9370529863465</v>
+        <v>1028.890452379605</v>
       </c>
       <c r="C45" t="n">
-        <v>412.0785555666301</v>
+        <v>853.031954959888</v>
       </c>
       <c r="D45" t="n">
-        <v>249.5152354679406</v>
+        <v>690.4686348611986</v>
       </c>
       <c r="E45" t="n">
-        <v>92.27069281954398</v>
+        <v>533.2240922128019</v>
       </c>
       <c r="F45" t="n">
-        <v>92.27069281954398</v>
+        <v>379.04606964929</v>
       </c>
       <c r="G45" t="n">
-        <v>92.27069281954398</v>
+        <v>238.9051243209795</v>
       </c>
       <c r="H45" t="n">
         <v>92.27069281954398</v>
@@ -7733,37 +7733,37 @@
         <v>1791.35062421531</v>
       </c>
       <c r="O45" t="n">
-        <v>2062.378175960832</v>
+        <v>2091.848227450212</v>
       </c>
       <c r="P45" t="n">
-        <v>2360.037520430339</v>
+        <v>2389.507571919719</v>
       </c>
       <c r="Q45" t="n">
-        <v>2373.819047990764</v>
+        <v>2403.289099480144</v>
       </c>
       <c r="R45" t="n">
-        <v>2373.819047990764</v>
+        <v>2403.289099480144</v>
       </c>
       <c r="S45" t="n">
-        <v>2150.828592316547</v>
+        <v>2343.930332204927</v>
       </c>
       <c r="T45" t="n">
-        <v>1930.265193106937</v>
+        <v>2123.366932995317</v>
       </c>
       <c r="U45" t="n">
-        <v>1714.901193349172</v>
+        <v>1908.002933237553</v>
       </c>
       <c r="V45" t="n">
-        <v>1485.092438610263</v>
+        <v>1678.194178498644</v>
       </c>
       <c r="W45" t="n">
-        <v>1237.240779105386</v>
+        <v>1678.194178498644</v>
       </c>
       <c r="X45" t="n">
-        <v>1002.025890776711</v>
+        <v>1442.979290169969</v>
       </c>
       <c r="Y45" t="n">
-        <v>787.4891304068785</v>
+        <v>1228.442529800137</v>
       </c>
     </row>
     <row r="46">
@@ -7797,43 +7797,43 @@
         <v>61.84</v>
       </c>
       <c r="J46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="K46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="L46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="M46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="N46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="O46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="P46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="Q46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="R46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="S46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="T46" t="n">
-        <v>120.4156216612533</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="U46" t="n">
-        <v>156.0968142995399</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="V46" t="n">
-        <v>143.8035716568973</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="W46" t="n">
         <v>104.0330566683016</v>
@@ -7967,13 +7967,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>306.2599628088302</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>532.2245521358337</v>
       </c>
       <c r="M2" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
         <v>477.2489580698352</v>
@@ -7985,7 +7985,7 @@
         <v>814.2870600406815</v>
       </c>
       <c r="Q2" t="n">
-        <v>615.8520732695737</v>
+        <v>189.0212843274853</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,25 +8201,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>581.9175466389624</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>884.2478695740924</v>
+        <v>668.2182504408672</v>
       </c>
       <c r="P5" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406851054</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8438,22 +8438,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>233.2813807819365</v>
+        <v>473.6327148598229</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814674</v>
@@ -8675,13 +8675,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>148.8262285640457</v>
       </c>
       <c r="K11" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,7 +8690,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>602.7693615519817</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8918,7 +8918,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>435.3966095009885</v>
+        <v>814</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,7 +8927,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>884.2478695740924</v>
+        <v>505.644479075081</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9152,7 +9152,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>64.42599844307665</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>814</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>884.2478695740924</v>
+        <v>505.644479075081</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,13 +9386,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,10 +9401,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>134.6738680171692</v>
+        <v>627.0604808351362</v>
       </c>
       <c r="P20" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
         <v>172.8226843274854</v>
@@ -9623,16 +9623,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>293.8645354141495</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
         <v>1096.663422488788</v>
@@ -9641,10 +9641,10 @@
         <v>884.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q23" t="n">
-        <v>172.8226843274854</v>
+        <v>237.2486827705622</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,7 +9863,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9875,13 +9875,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>827.3304336737069</v>
+        <v>843.247869574119</v>
       </c>
       <c r="P26" t="n">
-        <v>773.2870600407094</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>213.0301309040018</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,10 +10097,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10112,13 +10112,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>827.3304336736995</v>
+        <v>835.6876575496134</v>
       </c>
       <c r="P29" t="n">
-        <v>773.2870600407167</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>50.42570624509119</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>772.9999999999998</v>
+        <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>1060.271045550332</v>
+        <v>565.1026386843475</v>
       </c>
       <c r="N32" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>520.8080175723437</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406389485</v>
+        <v>773.2870600407226</v>
       </c>
       <c r="Q32" t="n">
-        <v>203.5880843275288</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,25 +10571,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>50.42570624509131</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>14.46944784831706</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>737.7156285650718</v>
       </c>
       <c r="M35" t="n">
-        <v>1027.972874281231</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741409</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407313</v>
+        <v>773.2870600407299</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10814,19 +10814,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>118.3011641460996</v>
       </c>
       <c r="M38" t="n">
-        <v>662.5632917884777</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741481</v>
       </c>
       <c r="P38" t="n">
-        <v>773.2870600407385</v>
+        <v>773.2870600407372</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11048,10 +11048,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>765.4397879755212</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11060,10 +11060,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>779.5627750726499</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407444</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11282,22 +11282,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>183.4348451165624</v>
+        <v>835.6876575496134</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
@@ -22703,7 +22703,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.66244969644795</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>5.662449696442479</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>5.662449696444568</v>
+        <v>5.662449696444583</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -23174,16 +23174,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.662449696447723</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>29.21007785423009</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -23223,22 +23223,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>14.5178835615053</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23277,7 +23277,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>199.187628204858</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23381,19 +23381,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
         <v>60.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G13" t="n">
         <v>20.04387284153003</v>
@@ -23411,13 +23411,13 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L13" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>295.6316114025499</v>
       </c>
       <c r="N13" t="n">
-        <v>346.1850752716849</v>
+        <v>203.9559039409364</v>
       </c>
       <c r="O13" t="n">
         <v>415.445564079015</v>
@@ -23426,7 +23426,7 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>375.2652747268922</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
         <v>501.6021279811511</v>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>148.5824408122632</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -23475,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>152.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23511,10 +23511,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T14" t="n">
-        <v>239.6732363275696</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -23660,13 +23660,13 @@
         <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>382.7066165981673</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>383.4694781537204</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23709,10 +23709,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.4306086145859922</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4306086145860206</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23855,7 +23855,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -23900,13 +23900,13 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>199.6877786647074</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.4306086145859922</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.430608614585708</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24131,16 +24131,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>430.4918320509147</v>
       </c>
       <c r="R22" t="n">
-        <v>69.8091295274528</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24183,7 +24183,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4306086145859922</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24365,19 +24365,19 @@
         <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>69.04626797189979</v>
       </c>
       <c r="Q25" t="n">
-        <v>400.3855738964583</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24411,22 +24411,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>98.18108525376776</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24456,10 +24456,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -24468,13 +24468,13 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>21.41409439602063</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>367.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -24596,10 +24596,10 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>153.4024400718014</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>346.1850752716849</v>
@@ -24614,7 +24614,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24645,25 +24645,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>35.06290239760591</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>35.72681969570087</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24702,7 +24702,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24803,16 +24803,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>22.9528500919632</v>
       </c>
       <c r="F31" t="n">
         <v>49.38285596774193</v>
@@ -24830,7 +24830,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L31" t="n">
         <v>198.5476281577792</v>
@@ -24851,10 +24851,10 @@
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>340.8632251862785</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S31" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25076,22 +25076,22 @@
         <v>229.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>85.5866114845816</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>434.839266425598</v>
+        <v>1.322948915185293</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25307,28 +25307,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>85.58661148455832</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>71.37347970285543</v>
+        <v>47.71401317082838</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25544,28 +25544,28 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>326.3973665406039</v>
+        <v>208.8479973216246</v>
       </c>
       <c r="S40" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,22 +25593,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>167.5808252291868</v>
       </c>
       <c r="C41" t="n">
-        <v>84.15964203174173</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>191.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>191.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>190.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -25641,13 +25641,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>37.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>281.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>373.6755817285639</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -25656,13 +25656,13 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>425.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>298.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>120.9698752289258</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>137.4664427423195</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25769,7 +25769,7 @@
         <v>32.04387284153003</v>
       </c>
       <c r="H43" t="n">
-        <v>15.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25814,7 +25814,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>13.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>34.44364543010755</v>
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>152.588324154612</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>262.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>223.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>217.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>217.8896287080119</v>
+        <v>175.5347474712544</v>
       </c>
       <c r="G44" t="n">
         <v>216.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>221.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25893,10 +25893,10 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>451.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>405.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -25921,13 +25921,13 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>152.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>138.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>145.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25960,7 +25960,7 @@
         <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>58.80344884713585</v>
+        <v>220.7988203621466</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>245.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26048,10 +26048,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>39.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>60.44364543010755</v>
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4734300.383694193</v>
+        <v>4734300.383694192</v>
       </c>
     </row>
     <row r="8">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6949574.763851718</v>
+        <v>6949574.763851719</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7645427.041364882</v>
+        <v>7645427.041364885</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8413400.101215739</v>
+        <v>8413400.101215744</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9179667.040546294</v>
+        <v>9179667.040546302</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9945933.979876855</v>
+        <v>9945933.979876857</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10619310.62414472</v>
+        <v>10619310.62414473</v>
       </c>
     </row>
     <row r="16">
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1416010.498272105</v>
+      </c>
+      <c r="C2" t="n">
         <v>1416010.498272106</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1416010.498272105</v>
       </c>
       <c r="D2" t="n">
         <v>1416010.498272106</v>
@@ -26296,16 +26296,16 @@
         <v>1252534.099523703</v>
       </c>
       <c r="K2" t="n">
-        <v>1252534.099523704</v>
+        <v>1252534.099523703</v>
       </c>
       <c r="L2" t="n">
-        <v>1379280.490794997</v>
+        <v>1379280.490794998</v>
       </c>
       <c r="M2" t="n">
         <v>1379280.490794998</v>
       </c>
       <c r="N2" t="n">
-        <v>1379280.490794998</v>
+        <v>1379280.490794997</v>
       </c>
       <c r="O2" t="n">
         <v>1215148.976618704</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>614247.5715792081</v>
+        <v>619095.9472656923</v>
       </c>
       <c r="C4" t="n">
-        <v>612495.6628399485</v>
+        <v>617344.0385264328</v>
       </c>
       <c r="D4" t="n">
-        <v>610741.3775271378</v>
+        <v>615589.7532136219</v>
       </c>
       <c r="E4" t="n">
-        <v>532123.603825271</v>
+        <v>536922.2846154375</v>
       </c>
       <c r="F4" t="n">
-        <v>556398.2196192667</v>
+        <v>561196.9004094332</v>
       </c>
       <c r="G4" t="n">
-        <v>581187.6277435899</v>
+        <v>585986.3085337563</v>
       </c>
       <c r="H4" t="n">
-        <v>579514.6928034928</v>
+        <v>584313.3735936591</v>
       </c>
       <c r="I4" t="n">
-        <v>577839.4224190661</v>
+        <v>582638.1032092324</v>
       </c>
       <c r="J4" t="n">
-        <v>520323.0592843113</v>
+        <v>524998.4738086243</v>
       </c>
       <c r="K4" t="n">
-        <v>518858.3176303694</v>
+        <v>523533.7321546826</v>
       </c>
       <c r="L4" t="n">
-        <v>581043.8351797319</v>
+        <v>585765.748114326</v>
       </c>
       <c r="M4" t="n">
-        <v>579313.7164781798</v>
+        <v>584035.6294127733</v>
       </c>
       <c r="N4" t="n">
-        <v>577581.1101536278</v>
+        <v>582303.0230882207</v>
       </c>
       <c r="O4" t="n">
-        <v>494869.5309141542</v>
+        <v>499544.9454384673</v>
       </c>
       <c r="P4" t="n">
-        <v>454063.7935190182</v>
+        <v>458739.2080433314</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>432116.1266928975</v>
+        <v>427267.7510064128</v>
       </c>
       <c r="C6" t="n">
-        <v>720396.0354321569</v>
+        <v>715547.6597456727</v>
       </c>
       <c r="D6" t="n">
-        <v>722150.3207449678</v>
+        <v>717301.9450584836</v>
       </c>
       <c r="E6" t="n">
-        <v>486252.3219384321</v>
+        <v>481453.6411482658</v>
       </c>
       <c r="F6" t="n">
-        <v>670653.4048498588</v>
+        <v>665854.7240596924</v>
       </c>
       <c r="G6" t="n">
-        <v>695016.4129090706</v>
+        <v>690217.7321189045</v>
       </c>
       <c r="H6" t="n">
-        <v>719089.3478491682</v>
+        <v>714290.6670590016</v>
       </c>
       <c r="I6" t="n">
-        <v>720764.6182335947</v>
+        <v>715965.9374434283</v>
       </c>
       <c r="J6" t="n">
-        <v>257401.1152393921</v>
+        <v>252725.7007150788</v>
       </c>
       <c r="K6" t="n">
-        <v>646961.8568933341</v>
+        <v>642286.4423690208</v>
       </c>
       <c r="L6" t="n">
-        <v>651574.1766152652</v>
+        <v>646852.2636806718</v>
       </c>
       <c r="M6" t="n">
-        <v>728504.2953168184</v>
+        <v>723782.3823822245</v>
       </c>
       <c r="N6" t="n">
-        <v>730236.90164137</v>
+        <v>725514.9887067764</v>
       </c>
       <c r="O6" t="n">
-        <v>580974.3487045501</v>
+        <v>576298.9341802369</v>
       </c>
       <c r="P6" t="n">
-        <v>616629.7391024231</v>
+        <v>611954.3245781101</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27005,10 +27005,10 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>-0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27436,16 +27436,16 @@
         <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>56.51176829727001</v>
+        <v>400</v>
       </c>
       <c r="D2" t="n">
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -27481,19 +27481,19 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>307.3903671255646</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
       </c>
       <c r="U2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>400</v>
@@ -27524,10 +27524,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>204.2843561227035</v>
       </c>
       <c r="G3" t="n">
-        <v>17.3083845693742</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>326.8237564296248</v>
+      </c>
+      <c r="C4" t="n">
         <v>400</v>
       </c>
-      <c r="C4" t="n">
-        <v>272.7252466480447</v>
-      </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
@@ -27606,13 +27606,13 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
@@ -27642,16 +27642,16 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>384.4790176045187</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27676,7 +27676,7 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,13 +27718,13 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
-        <v>56.5117682972699</v>
+        <v>400</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27736,7 +27736,7 @@
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>400</v>
+        <v>157.3092074428799</v>
       </c>
       <c r="Y5" t="n">
         <v>400</v>
@@ -27749,13 +27749,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>235.8685316061258</v>
       </c>
       <c r="C6" t="n">
-        <v>76.45355315257615</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27828,22 +27828,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>398.4349853031635</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>387.1332798435803</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27855,7 +27855,7 @@
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T7" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U7" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V7" t="n">
         <v>400</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>400</v>
-      </c>
-      <c r="U7" t="n">
-        <v>400</v>
-      </c>
-      <c r="V7" t="n">
-        <v>199.1703102162162</v>
-      </c>
-      <c r="W7" t="n">
-        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27922,49 +27922,49 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>250.8785988282945</v>
+      </c>
+      <c r="S8" t="n">
+        <v>56.51176829727007</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>400</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>307.3903671255646</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -27973,7 +27973,7 @@
         <v>400</v>
       </c>
       <c r="X8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>400</v>
@@ -27989,10 +27989,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>251.3119749597992</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28046,13 +28046,13 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>342.2743756165772</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,34 +28065,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>379.1217985924877</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>276.3639593338141</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
+        <v>228.7711261016186</v>
+      </c>
+      <c r="I10" t="n">
         <v>400</v>
-      </c>
-      <c r="I10" t="n">
-        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28244,10 +28244,10 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J12" t="n">
-        <v>78.91122027701076</v>
+        <v>19.11687125883891</v>
       </c>
       <c r="K12" t="n">
         <v>225</v>
@@ -28268,7 +28268,7 @@
         <v>225</v>
       </c>
       <c r="Q12" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R12" t="n">
         <v>225</v>
@@ -28490,19 +28490,19 @@
         <v>251</v>
       </c>
       <c r="L15" t="n">
-        <v>166.1982915220776</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>166.1982915220775</v>
       </c>
       <c r="O15" t="n">
         <v>251</v>
       </c>
       <c r="P15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>251</v>
@@ -28724,25 +28724,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>261.5913251766236</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>155.6705902671031</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28967,16 +28967,16 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>155.6705902671031</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="O21" t="n">
-        <v>155.6705902671032</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>279</v>
@@ -29195,22 +29195,22 @@
         <v>279</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>279</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>155.6705902671032</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>155.6705902671033</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -29438,7 +29438,7 @@
         <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="M27" t="n">
         <v>225</v>
@@ -29447,7 +29447,7 @@
         <v>225</v>
       </c>
       <c r="O27" t="n">
-        <v>225</v>
+        <v>19.11687125883898</v>
       </c>
       <c r="P27" t="n">
         <v>225</v>
@@ -29666,10 +29666,10 @@
         <v>225</v>
       </c>
       <c r="I30" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J30" t="n">
-        <v>26.99048536749061</v>
+        <v>225</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
@@ -29681,7 +29681,7 @@
         <v>225</v>
       </c>
       <c r="N30" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O30" t="n">
         <v>225</v>
@@ -29824,7 +29824,7 @@
         <v>291</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>141.6245682972704</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29872,7 +29872,7 @@
         <v>291</v>
       </c>
       <c r="Y32" t="n">
-        <v>282.5434086145857</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33">
@@ -29903,10 +29903,10 @@
         <v>291</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>291</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -29918,10 +29918,10 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>127.8102101760007</v>
+        <v>53.93659606734943</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -29961,7 +29961,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
       <c r="C34" t="n">
         <v>291</v>
@@ -30061,7 +30061,7 @@
         <v>291</v>
       </c>
       <c r="I35" t="n">
-        <v>150.0811596826846</v>
+        <v>141.6245682972704</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>242.4220074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
         <v>291</v>
@@ -30140,7 +30140,7 @@
         <v>291</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>291</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30152,7 +30152,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>9.889475266480332</v>
+        <v>291</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -30161,10 +30161,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>291</v>
+        <v>227.0158611578287</v>
       </c>
       <c r="R36" t="n">
         <v>291</v>
@@ -30377,25 +30377,25 @@
         <v>291</v>
       </c>
       <c r="I39" t="n">
+        <v>227.0158611578287</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>291</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>227.0158611578287</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>291.0000000000276</v>
+        <v>291</v>
       </c>
       <c r="C40" t="n">
         <v>291</v>
@@ -30632,10 +30632,10 @@
         <v>213</v>
       </c>
       <c r="O42" t="n">
+        <v>158.597814363541</v>
+      </c>
+      <c r="P42" t="n">
         <v>213</v>
-      </c>
-      <c r="P42" t="n">
-        <v>175.4293290185695</v>
       </c>
       <c r="Q42" t="n">
         <v>213</v>
@@ -30696,7 +30696,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>35.26894883590776</v>
+        <v>65.00462472645802</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30869,7 +30869,7 @@
         <v>187</v>
       </c>
       <c r="O45" t="n">
-        <v>32.30818188060952</v>
+        <v>62.07591065776113</v>
       </c>
       <c r="P45" t="n">
         <v>187</v>
@@ -30933,7 +30933,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>94.43624344323428</v>
+        <v>77.88819799580841</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -30966,7 +30966,7 @@
         <v>187</v>
       </c>
       <c r="U46" t="n">
-        <v>187</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V46" t="n">
         <v>187</v>
@@ -34746,7 +34746,7 @@
         <v>814</v>
       </c>
       <c r="K2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>814</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>39.70995609254612</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -34892,13 +34892,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -34928,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>22.10553790166324</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34946,7 +34946,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,7 +34983,7 @@
         <v>814</v>
       </c>
       <c r="K5" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
@@ -34998,7 +34998,7 @@
         <v>814</v>
       </c>
       <c r="P5" t="n">
-        <v>814</v>
+        <v>814.0000000000036</v>
       </c>
       <c r="Q5" t="n">
         <v>814</v>
@@ -35114,22 +35114,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>112.898767247608</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>142.0894070020503</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
@@ -35141,7 +35141,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35223,7 +35223,7 @@
         <v>814.0000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M8" t="n">
         <v>814</v>
@@ -35351,34 +35351,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>106.396551944443</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>31.32008649228405</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,13 +35454,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,7 +35469,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>532.5214919778892</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35530,10 +35530,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>204.1198265146865</v>
+        <v>144.3254774965146</v>
       </c>
       <c r="K12" t="n">
         <v>416.1038546407913</v>
@@ -35554,7 +35554,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35697,7 +35697,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>435.3966095009885</v>
+        <v>814</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,7 +35706,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>814</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35776,19 +35776,19 @@
         <v>442.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>440.2896668707646</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>86.95004216450428</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>134.6265501086548</v>
+        <v>300.8248416307323</v>
       </c>
       <c r="O15" t="n">
         <v>492.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>364.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
         <v>77.92073490952041</v>
@@ -35931,7 +35931,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>64.42599844307665</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>814</v>
@@ -35943,13 +35943,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>814</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36010,25 +36010,25 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>274.091375348687</v>
+        <v>535.6827005253105</v>
       </c>
       <c r="M18" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
-        <v>290.2971403757579</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,13 +36165,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,10 +36180,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>64.42599844307681</v>
+        <v>556.8126112610438</v>
       </c>
       <c r="P20" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36253,16 +36253,16 @@
         <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>86.95004216450428</v>
+        <v>242.6206324316074</v>
       </c>
       <c r="N21" t="n">
-        <v>134.6265501086548</v>
+        <v>413.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>397.1276121698496</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
         <v>105.9207349095204</v>
@@ -36402,16 +36402,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>258.8215291690591</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
         <v>619.4144644189528</v>
@@ -36420,10 +36420,10 @@
         <v>814</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>64.42599844307681</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36481,22 +36481,22 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>429.7619656157902</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>134.6265501086548</v>
+        <v>413.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>241.4570219027464</v>
+        <v>397.1276121698497</v>
       </c>
       <c r="P24" t="n">
         <v>113.6660045146532</v>
@@ -36642,7 +36642,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -36654,13 +36654,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>757.0825640996145</v>
+        <v>773.0000000000266</v>
       </c>
       <c r="P26" t="n">
-        <v>773.000000000028</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>40.20744657651642</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36724,7 +36724,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>293.2082466075261</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
         <v>311.9500421645043</v>
@@ -36733,7 +36733,7 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
-        <v>466.4570219027464</v>
+        <v>260.5738931615854</v>
       </c>
       <c r="P27" t="n">
         <v>338.6660045146532</v>
@@ -36876,10 +36876,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -36891,13 +36891,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>757.0825640996071</v>
+        <v>765.439787975521</v>
       </c>
       <c r="P29" t="n">
-        <v>773.0000000000352</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,10 +36952,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
-        <v>152.1990916051663</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
@@ -36967,7 +36967,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O30" t="n">
         <v>466.4570219027464</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773.0000000000425</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320761845</v>
+        <v>727.107932076386</v>
       </c>
       <c r="L32" t="n">
-        <v>773.0000000000001</v>
+        <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000425</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000425</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000425</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="P32" t="n">
-        <v>773</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="Q32" t="n">
-        <v>773.0000000000425</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,10 +37189,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J33" t="n">
-        <v>125.2086062376757</v>
+        <v>416.2086062376757</v>
       </c>
       <c r="K33" t="n">
         <v>191.1038546407913</v>
@@ -37204,10 +37204,10 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>425.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
-        <v>369.2672320787471</v>
+        <v>295.3936179700958</v>
       </c>
       <c r="P33" t="n">
         <v>113.6660045146532</v>
@@ -37247,7 +37247,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.886199662921342</v>
+        <v>3.886199662945266</v>
       </c>
       <c r="C34" t="n">
         <v>18.27475335195533</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773.0000000000498</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320762286</v>
+        <v>762.3923035111844</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>737.7156285650718</v>
       </c>
       <c r="M35" t="n">
-        <v>773.0000000000498</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000498</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000498</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000498</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="Q35" t="n">
-        <v>773.0000000000498</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,7 +37426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
@@ -37438,7 +37438,7 @@
         <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
-        <v>96.83951743098461</v>
+        <v>377.9500421645043</v>
       </c>
       <c r="N36" t="n">
         <v>134.6265501086548</v>
@@ -37447,10 +37447,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>404.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>117.9207349095204</v>
+        <v>53.93659606734907</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773.0000000000571</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320762617</v>
+        <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>727.1079320759262</v>
       </c>
       <c r="M38" t="n">
-        <v>773.0000000000571</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000571</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000571</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000571</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="Q38" t="n">
-        <v>773.0000000000571</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37663,7 +37663,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>73.87361410865147</v>
+        <v>9.889475266480202</v>
       </c>
       <c r="J39" t="n">
         <v>125.2086062376757</v>
@@ -37681,7 +37681,7 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
-        <v>468.4728830605751</v>
+        <v>532.4570219027464</v>
       </c>
       <c r="P39" t="n">
         <v>113.6660045146532</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.886199662948904</v>
+        <v>3.886199662921342</v>
       </c>
       <c r="C40" t="n">
         <v>18.27475335195533</v>
@@ -37827,10 +37827,10 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>765.4397879755212</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -37839,10 +37839,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>709.3149054985574</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>773.000000000063</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37918,10 +37918,10 @@
         <v>347.6265501086548</v>
       </c>
       <c r="O42" t="n">
-        <v>454.4570219027464</v>
+        <v>400.0548362662873</v>
       </c>
       <c r="P42" t="n">
-        <v>289.0953335332227</v>
+        <v>326.6660045146532</v>
       </c>
       <c r="Q42" t="n">
         <v>39.92073490952041</v>
@@ -37982,7 +37982,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>29.73567589055027</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38061,22 +38061,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>113.18697554247</v>
+        <v>765.439787975521</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -38155,7 +38155,7 @@
         <v>321.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>273.7652037833559</v>
+        <v>303.5329325605075</v>
       </c>
       <c r="P45" t="n">
         <v>300.6660045146532</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>59.16729460732652</v>
+        <v>42.61924915990064</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>36.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
